--- a/data/trans_dic/P16A20_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,71</t>
+          <t>0,56; 3,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,84</t>
+          <t>4,74; 9,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,58</t>
+          <t>2,94; 5,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,51</t>
+          <t>0,34; 2,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,49</t>
+          <t>4,6; 8,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,87</t>
+          <t>2,56; 4,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,95</t>
+          <t>0,59; 2,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,87</t>
+          <t>5,48; 9,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,18</t>
+          <t>3,39; 6,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,82</t>
+          <t>3,93; 9,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,43</t>
+          <t>2,79; 5,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,88</t>
+          <t>0,74; 6,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,61</t>
+          <t>6,67; 11,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,12</t>
+          <t>4,36; 8,08</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,24</t>
+          <t>0,29; 2,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,99</t>
+          <t>7,79; 13,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,03</t>
+          <t>4,15; 6,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,24</t>
+          <t>0,94; 4,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 66,75</t>
+          <t>10,82; 66,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 48,66</t>
+          <t>6,47; 44,16</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,93</t>
+          <t>0,34; 1,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,15</t>
+          <t>6,09; 10,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,18</t>
+          <t>2,39; 5,25</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,81</t>
+          <t>0,91; 1,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,89; 28,24</t>
+          <t>7,87; 32,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 17,33</t>
+          <t>4,53; 17,53</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2142</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1827; 11550</t>
+          <t>1757; 11340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2095</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2161</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14035; 28492</t>
+          <t>13719; 27987</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2024</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17796; 33534</t>
+          <t>17675; 34998</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1987</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2227; 13007</t>
+          <t>1774; 12913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1981</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22989; 43598</t>
+          <t>23656; 45092</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27349; 50187</t>
+          <t>26366; 48947</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1869</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1573; 9332</t>
+          <t>1866; 9130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2051</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1836</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18753; 34445</t>
+          <t>19128; 34588</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22426; 41110</t>
+          <t>22552; 40564</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1941</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2026</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3650</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1836</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17718; 41976</t>
+          <t>18711; 43670</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21939; 42797</t>
+          <t>21965; 43900</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1272; 12297</t>
+          <t>1317; 11570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1874</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1796</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13593; 24194</t>
+          <t>13896; 24471</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1860</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16995; 31428</t>
+          <t>16884; 31258</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>484; 6037</t>
+          <t>775; 5636</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1857</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19350; 33393</t>
+          <t>20013; 33605</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22279; 37039</t>
+          <t>21878; 36566</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6172; 26497</t>
+          <t>5838; 27722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2004</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>95298; 566469</t>
+          <t>91829; 566868</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2075</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94573; 716659</t>
+          <t>95265; 650464</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1961</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3871; 17932</t>
+          <t>3158; 18500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2082</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42842; 72522</t>
+          <t>43570; 75828</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 1977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41011; 85123</t>
+          <t>39318; 86310</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30900; 62529</t>
+          <t>31327; 61801</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>288444; 1032918</t>
+          <t>287815; 1179965</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>323603; 1233134</t>
+          <t>322547; 1247335</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A20_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,64</t>
+          <t>0,52; 3,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,66</t>
+          <t>4,39; 8,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,82</t>
+          <t>2,76; 5,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,5</t>
+          <t>0,35; 2,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,78</t>
+          <t>4,36; 7,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,75</t>
+          <t>2,63; 4,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,89</t>
+          <t>0,51; 3,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,91</t>
+          <t>5,52; 9,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,1</t>
+          <t>3,52; 6,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,18</t>
+          <t>5,74; 10,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,57</t>
+          <t>3,19; 5,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,47</t>
+          <t>0,37; 5,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,75</t>
+          <t>6,58; 11,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,08</t>
+          <t>4,17; 7,47</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,09</t>
+          <t>0,19; 2,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 13,07</t>
+          <t>7,57; 13,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,94</t>
+          <t>4,19; 6,89</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,44</t>
+          <t>0,94; 3,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,82; 66,8</t>
+          <t>10,31; 14,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 44,16</t>
+          <t>6,25; 8,85</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,99</t>
+          <t>0,78; 2,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 10,61</t>
+          <t>5,44; 8,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,25</t>
+          <t>3,53; 5,2</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,79</t>
+          <t>0,97; 1,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,87; 32,27</t>
+          <t>7,6; 9,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 17,53</t>
+          <t>4,51; 5,36</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>24213</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1757; 11340</t>
+          <t>1647; 9950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13719; 27987</t>
+          <t>13888; 27484</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17675; 34998</t>
+          <t>17505; 32968</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37656</t>
+          <t>38251</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1774; 12913</t>
+          <t>1868; 11673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23656; 45092</t>
+          <t>23771; 43312</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26366; 48947</t>
+          <t>28263; 52910</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>30439</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1866; 9130</t>
+          <t>1599; 9509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19128; 34588</t>
+          <t>19657; 34771</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22552; 40564</t>
+          <t>23681; 41077</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>34061</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18711; 43670</t>
+          <t>24226; 42733</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21965; 43900</t>
+          <t>25329; 44756</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>24195</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1317; 11570</t>
+          <t>751; 11811</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13896; 24471</t>
+          <t>14936; 26379</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16884; 31258</t>
+          <t>18045; 32298</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26108</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28188</t>
+          <t>29056</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>775; 5636</t>
+          <t>509; 5606</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20013; 33605</t>
+          <t>19972; 34470</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21878; 36566</t>
+          <t>22402; 36803</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>279061</t>
+          <t>94858</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>291388</t>
+          <t>108269</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5838; 27722</t>
+          <t>6787; 27435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91829; 566868</t>
+          <t>79511; 112742</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>95265; 650464</t>
+          <t>93138; 131904</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>54555</t>
+          <t>58205</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>64714</t>
+          <t>69979</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3158; 18500</t>
+          <t>6255; 19124</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>43570; 75828</t>
+          <t>45175; 71502</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>39318; 86310</t>
+          <t>57395; 84593</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>531377</t>
+          <t>358463</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31327; 61801</t>
+          <t>34212; 63640</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>287815; 1179965</t>
+          <t>283571; 344144</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>322547; 1247335</t>
+          <t>327281; 389166</t>
         </is>
       </c>
     </row>
